--- a/r5-core-50-Gemeindekennziffer/StructureDefinition-at-core-extendedContactDetail.xlsx
+++ b/r5-core-50-Gemeindekennziffer/StructureDefinition-at-core-extendedContactDetail.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="371" uniqueCount="134">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="371" uniqueCount="135">
   <si>
     <t>Property</t>
   </si>
@@ -24,7 +24,7 @@
     <t>URL</t>
   </si>
   <si>
-    <t>http://hl7.at/fhir/HL7ATCoreProfiles/5.0.0/StructureDefinition/at-core-extendedContactDetail</t>
+    <t>https://fhir.hl7.at/core/r5/StructureDefinition/at-core-extendedContactDetail</t>
   </si>
   <si>
     <t>Version</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-09-07T12:16:57+00:00</t>
+    <t>2026-10-13T08:41:05+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -386,7 +386,7 @@
     <t>ExtendedContactDetail.address</t>
   </si>
   <si>
-    <t xml:space="preserve">Address {http://hl7.at/fhir/HL7ATCoreProfiles/5.0.0/StructureDefinition/at-core-address}
+    <t xml:space="preserve">Address {https://fhir.hl7.at/core/r5/StructureDefinition/at-core-address}
 </t>
   </si>
   <si>
@@ -399,10 +399,14 @@
     <t>More than 1 address would be for different purposes, and thus should be entered as a different entry,.</t>
   </si>
   <si>
+    <t>ele-1:All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
+at-addr-1:If the extension for street name is used then the value for line must not be empty {line.all($this.extension('http://hl7.org/fhir/StructureDefinition/iso21090-ADXP-streetName').empty() or $this.hasValue())}at-addr-2:If the extension for street number is used then the value for line must not be empty {line.all($this.extension('http://hl7.org/fhir/StructureDefinition/iso21090-ADXP-houseNumber').empty() or $this.hasValue())}at-addr-3:If the extension for floor/door number is used then the value for line must not be empty {line.all($this.extension('http://hl7.org/fhir/StructureDefinition/iso21090-ADXP-additionalLocator').empty() or $this.hasValue())}</t>
+  </si>
+  <si>
     <t>ExtendedContactDetail.organization</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(http://hl7.at/fhir/HL7ATCoreProfiles/5.0.0/StructureDefinition/at-core-organization)
+    <t xml:space="preserve">Reference(https://fhir.hl7.at/core/r5/StructureDefinition/at-core-organization)
 </t>
   </si>
   <si>
@@ -751,7 +755,7 @@
     <col min="8" max="8" width="13.953125" customWidth="true" bestFit="true"/>
     <col min="9" max="9" width="11.3671875" customWidth="true" bestFit="true"/>
     <col min="10" max="10" width="20.703125" customWidth="true" bestFit="true"/>
-    <col min="11" max="11" width="74.19140625" customWidth="true" bestFit="true"/>
+    <col min="11" max="11" width="61.53125" customWidth="true" bestFit="true"/>
     <col min="12" max="12" width="100.703125" customWidth="true" bestFit="true"/>
     <col min="13" max="13" width="100.703125" customWidth="true" bestFit="true"/>
     <col min="14" max="14" width="100.703125" customWidth="true" bestFit="true"/>
@@ -1617,7 +1621,7 @@
         <v>21</v>
       </c>
       <c r="AJ8" t="s" s="2">
-        <v>81</v>
+        <v>124</v>
       </c>
       <c r="AK8" t="s" s="2">
         <v>21</v>
@@ -1625,10 +1629,10 @@
     </row>
     <row r="9">
       <c r="A9" t="s" s="2">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="B9" t="s" s="2">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="C9" s="2"/>
       <c r="D9" t="s" s="2">
@@ -1651,17 +1655,17 @@
         <v>102</v>
       </c>
       <c r="K9" t="s" s="2">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="L9" t="s" s="2">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="M9" t="s" s="2">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="N9" s="2"/>
       <c r="O9" t="s" s="2">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="P9" t="s" s="2">
         <v>21</v>
@@ -1710,7 +1714,7 @@
         <v>21</v>
       </c>
       <c r="AF9" t="s" s="2">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="AG9" t="s" s="2">
         <v>75</v>
@@ -1730,10 +1734,10 @@
     </row>
     <row r="10">
       <c r="A10" t="s" s="2">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="B10" t="s" s="2">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="C10" s="2"/>
       <c r="D10" t="s" s="2">
@@ -1756,16 +1760,16 @@
         <v>102</v>
       </c>
       <c r="K10" t="s" s="2">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="L10" t="s" s="2">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="M10" t="s" s="2">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="N10" t="s" s="2">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="O10" s="2"/>
       <c r="P10" t="s" s="2">
@@ -1815,7 +1819,7 @@
         <v>21</v>
       </c>
       <c r="AF10" t="s" s="2">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="AG10" t="s" s="2">
         <v>75</v>
